--- a/data/football/exports/reporting/football_model_performance_dashboard.xlsx
+++ b/data/football/exports/reporting/football_model_performance_dashboard.xlsx
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:42</t>
+          <t>2026-05-24 05:45:51</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:49:39</t>
+          <t>2026-05-24 05:44:54</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:39</t>
+          <t>2026-05-24 05:45:50</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -8667,31 +8667,31 @@
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AH93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI93" t="n">
-        <v>0.724</v>
+        <v>0.757</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.478</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AK93" t="n">
-        <v>0.83</v>
+        <v>0.863</v>
       </c>
       <c r="AL93" t="n">
-        <v>0.898</v>
+        <v>0.867</v>
       </c>
       <c r="AM93" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AN93" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AO93" t="n">
-        <v>2.167</v>
+        <v>2.333</v>
       </c>
     </row>
     <row r="94">
@@ -8821,31 +8821,31 @@
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.648</v>
+        <v>0.631</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.426</v>
+        <v>0.408</v>
       </c>
       <c r="AK95" t="n">
-        <v>0.718</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AL95" t="n">
-        <v>0.847</v>
+        <v>0.854</v>
       </c>
       <c r="AM95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AN95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO95" t="n">
-        <v>1.889</v>
+        <v>1.857</v>
       </c>
     </row>
     <row r="96">
@@ -8898,28 +8898,28 @@
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AH96" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AI96" t="n">
-        <v>0.675</v>
+        <v>0.742</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0.396</v>
+        <v>0.369</v>
       </c>
       <c r="AK96" t="n">
-        <v>0.786</v>
+        <v>0.954</v>
       </c>
       <c r="AL96" t="n">
-        <v>0.889</v>
+        <v>0.923</v>
       </c>
       <c r="AM96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AN96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO96" t="n">
         <v>2</v>
@@ -9054,16 +9054,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C:\Users\USER\Desktop\Python Projects\HexagrandHouse_VSCode\data\football\exports\models\football_goals_model_predictions.xlsx</t>
+          <t>/home/runner/work/HexagrandHouse/HexagrandHouse/data/football/exports/models/football_goals_model_predictions.xlsx</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:45:00</t>
+          <t>2026-05-24 05:43:13</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.36</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="3">
@@ -9077,16 +9077,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C:\Users\USER\Desktop\Python Projects\HexagrandHouse_VSCode\data\football\exports\models\football_corners_model_predictions.xlsx</t>
+          <t>/home/runner/work/HexagrandHouse/HexagrandHouse/data/football/exports/models/football_corners_model_predictions.xlsx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:47:08</t>
+          <t>2026-05-24 05:43:54</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="4">
@@ -9100,16 +9100,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C:\Users\USER\Desktop\Python Projects\HexagrandHouse_VSCode\data\football\exports\models\football_result_model_predictions.xlsx</t>
+          <t>/home/runner/work/HexagrandHouse/HexagrandHouse/data/football/exports/models/football_result_model_predictions.xlsx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:46:28</t>
+          <t>2026-05-24 05:43:40</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.66</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="5">
@@ -9123,16 +9123,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C:\Users\USER\Desktop\Python Projects\HexagrandHouse_VSCode\data\football\exports\predictions\football_ensemble_predictions.xlsx</t>
+          <t>/home/runner/work/HexagrandHouse/HexagrandHouse/data/football/exports/predictions/football_ensemble_predictions.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:28</t>
+          <t>2026-05-24 05:45:48</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17.77</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="6">
@@ -9146,16 +9146,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C:\Users\USER\Desktop\Python Projects\HexagrandHouse_VSCode\data\football\exports\predictions\football_fixture_predictions.xlsx</t>
+          <t>/home/runner/work/HexagrandHouse/HexagrandHouse/data/football/exports/predictions/football_fixture_predictions.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:51:40</t>
+          <t>2026-05-24 05:45:50</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/data/football/exports/reporting/football_model_performance_dashboard.xlsx
+++ b/data/football/exports/reporting/football_model_performance_dashboard.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57933</v>
+        <v>57980</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27210</v>
+        <v>27257</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57932</v>
+        <v>57979</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75298</v>
+        <v>75345</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6909999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:45:51</t>
+          <t>2026-05-25 14:43:06</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57933</v>
+        <v>57980</v>
       </c>
       <c r="E2" t="n">
         <v>0.778</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57933</v>
+        <v>57980</v>
       </c>
       <c r="E3" t="n">
         <v>0.596</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57933</v>
+        <v>57980</v>
       </c>
       <c r="E4" t="n">
         <v>0.386</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57933</v>
+        <v>57980</v>
       </c>
       <c r="E5" t="n">
         <v>0.611</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27210</v>
+        <v>27257</v>
       </c>
       <c r="E6" t="n">
         <v>0.885</v>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27210</v>
+        <v>27257</v>
       </c>
       <c r="E7" t="n">
         <v>0.775</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27210</v>
+        <v>27257</v>
       </c>
       <c r="E8" t="n">
         <v>0.67</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27210</v>
+        <v>27257</v>
       </c>
       <c r="E9" t="n">
         <v>0.574</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57932</v>
+        <v>57979</v>
       </c>
       <c r="E10" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75298</v>
+        <v>75345</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -953,225 +953,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:44:54</t>
+          <t>2026-05-25 14:42:10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Fixtures Predicted</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>32</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Leagues</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Rows With Odds</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>32</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Rows With Corners Prediction</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>32</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Elite Predictions</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>24</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Average Ensemble Confidence</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Earliest Fixture</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Latest Fixture</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Future Fixtures</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Fixture Prediction</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Generated At</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-05-24 05:45:50</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1184,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO97"/>
+  <dimension ref="A1:AF92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1348,51 +1135,6 @@
           <t>NoClearEdgeRate</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>ElitePredictions</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>AvgEnsembleConfidence</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>AvgResultProbability</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>AvgGoalsProbability</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>AvgCornersProbability</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>RowsWithCornersPrediction</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>RowsWithOdds</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>AvgSignalCount</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1411,7 +1153,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="E2" t="n">
         <v>2.811</v>
@@ -1426,16 +1168,16 @@
         <v>0.638</v>
       </c>
       <c r="I2" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="J2" t="n">
-        <v>0.518</v>
+        <v>0.519</v>
       </c>
       <c r="K2" t="n">
         <v>0.6820000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>0.518</v>
+        <v>0.519</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1461,15 +1203,6 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1488,7 +1221,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E3" t="n">
         <v>2.957</v>
@@ -1503,16 +1236,16 @@
         <v>0.667</v>
       </c>
       <c r="I3" t="n">
-        <v>0.788</v>
+        <v>0.789</v>
       </c>
       <c r="J3" t="n">
         <v>0.538</v>
       </c>
       <c r="K3" t="n">
-        <v>0.645</v>
+        <v>0.647</v>
       </c>
       <c r="L3" t="n">
-        <v>0.54</v>
+        <v>0.541</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1538,15 +1271,6 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1615,15 +1339,6 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1692,15 +1407,6 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1719,10 +1425,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E6" t="n">
-        <v>2.542</v>
+        <v>2.54</v>
       </c>
       <c r="F6" t="n">
         <v>0.754</v>
@@ -1740,7 +1446,7 @@
         <v>0.503</v>
       </c>
       <c r="K6" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="L6" t="n">
         <v>0.489</v>
@@ -1769,15 +1475,6 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1846,15 +1543,6 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1923,15 +1611,6 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1950,7 +1629,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E9" t="n">
         <v>2.608</v>
@@ -1974,7 +1653,7 @@
         <v>0.751</v>
       </c>
       <c r="L9" t="n">
-        <v>0.525</v>
+        <v>0.526</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2000,15 +1679,6 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2077,15 +1747,6 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2154,15 +1815,6 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2231,15 +1883,6 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2308,15 +1951,6 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2385,15 +2019,6 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2462,15 +2087,6 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2539,15 +2155,6 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2616,15 +2223,6 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2693,15 +2291,6 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2770,15 +2359,6 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2797,28 +2377,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1826</v>
+        <v>1837</v>
       </c>
       <c r="E20" t="n">
-        <v>2.341</v>
+        <v>2.345</v>
       </c>
       <c r="F20" t="n">
-        <v>0.715</v>
+        <v>0.716</v>
       </c>
       <c r="G20" t="n">
         <v>0.54</v>
       </c>
       <c r="H20" t="n">
-        <v>0.545</v>
+        <v>0.546</v>
       </c>
       <c r="I20" t="n">
-        <v>0.627</v>
+        <v>0.628</v>
       </c>
       <c r="J20" t="n">
-        <v>0.569</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="L20" t="n">
         <v>0.535</v>
@@ -2847,15 +2427,6 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2924,15 +2495,6 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3001,15 +2563,6 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3078,15 +2631,6 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3155,15 +2699,6 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3232,15 +2767,6 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3309,15 +2835,6 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3386,15 +2903,6 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3463,15 +2971,6 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3540,15 +3039,6 @@
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3617,15 +3107,6 @@
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3694,15 +3175,6 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3771,15 +3243,6 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3848,15 +3311,6 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3925,15 +3379,6 @@
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4002,15 +3447,6 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4079,15 +3515,6 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4156,15 +3583,6 @@
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4183,7 +3601,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -4199,7 +3617,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>9.923999999999999</v>
+        <v>9.926</v>
       </c>
       <c r="O38" t="n">
         <v>0.901</v>
@@ -4211,7 +3629,7 @@
         <v>0.6830000000000001</v>
       </c>
       <c r="R38" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="S38" t="n">
         <v>0.657</v>
@@ -4220,7 +3638,7 @@
         <v>0.541</v>
       </c>
       <c r="U38" t="n">
-        <v>0.502</v>
+        <v>0.503</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
@@ -4233,15 +3651,6 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4260,7 +3669,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -4276,10 +3685,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>10.233</v>
+        <v>10.232</v>
       </c>
       <c r="O39" t="n">
-        <v>0.917</v>
+        <v>0.916</v>
       </c>
       <c r="P39" t="n">
         <v>0.8080000000000001</v>
@@ -4291,13 +3700,13 @@
         <v>0.774</v>
       </c>
       <c r="S39" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="T39" t="n">
         <v>0.57</v>
       </c>
       <c r="U39" t="n">
-        <v>0.52</v>
+        <v>0.519</v>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
@@ -4310,15 +3719,6 @@
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4387,15 +3787,6 @@
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4464,15 +3855,6 @@
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4491,7 +3873,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -4519,13 +3901,13 @@
         <v>0.642</v>
       </c>
       <c r="R42" t="n">
-        <v>0.676</v>
+        <v>0.674</v>
       </c>
       <c r="S42" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T42" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="U42" t="n">
         <v>0.574</v>
@@ -4541,15 +3923,6 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4618,15 +3991,6 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4695,15 +4059,6 @@
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4722,7 +4077,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -4738,28 +4093,28 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>9.430999999999999</v>
+        <v>9.432</v>
       </c>
       <c r="O45" t="n">
         <v>0.869</v>
       </c>
       <c r="P45" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="Q45" t="n">
         <v>0.654</v>
       </c>
       <c r="R45" t="n">
-        <v>0.713</v>
+        <v>0.712</v>
       </c>
       <c r="S45" t="n">
-        <v>0.592</v>
+        <v>0.591</v>
       </c>
       <c r="T45" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="U45" t="n">
-        <v>0.543</v>
+        <v>0.544</v>
       </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
@@ -4772,15 +4127,6 @@
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4849,15 +4195,6 @@
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4926,15 +4263,6 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5003,15 +4331,6 @@
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5080,15 +4399,6 @@
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5157,15 +4467,6 @@
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5234,15 +4535,6 @@
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5311,15 +4603,6 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5388,15 +4671,6 @@
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5465,15 +4739,6 @@
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5492,7 +4757,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1826</v>
+        <v>1837</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -5520,13 +4785,13 @@
         <v>0.643</v>
       </c>
       <c r="R55" t="n">
-        <v>0.702</v>
+        <v>0.703</v>
       </c>
       <c r="S55" t="n">
-        <v>0.576</v>
+        <v>0.578</v>
       </c>
       <c r="T55" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="U55" t="n">
         <v>0.555</v>
@@ -5542,15 +4807,6 @@
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5619,15 +4875,6 @@
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5646,7 +4893,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -5670,47 +4917,38 @@
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="W57" t="n">
         <v>0.278</v>
       </c>
       <c r="X57" t="n">
-        <v>0.328</v>
+        <v>0.327</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="AB57" t="n">
         <v>0.311</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.659</v>
+        <v>0.661</v>
       </c>
       <c r="AD57" t="n">
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="AF57" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5729,7 +4967,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
@@ -5753,7 +4991,7 @@
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="W58" t="n">
         <v>0.275</v>
@@ -5762,38 +5000,29 @@
         <v>0.328</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.506</v>
+        <v>0.505</v>
       </c>
       <c r="Z58" t="n">
         <v>0.445</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.24</v>
+        <v>0.241</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.315</v>
+        <v>0.314</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.659</v>
+        <v>0.66</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="AF58" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5868,15 +5097,6 @@
       <c r="AF59" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5951,15 +5171,6 @@
       <c r="AF60" t="n">
         <v>0</v>
       </c>
-      <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5978,7 +5189,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
@@ -6011,19 +5222,19 @@
         <v>0.326</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.482</v>
+        <v>0.483</v>
       </c>
       <c r="Z61" t="n">
         <v>0.407</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.275</v>
+        <v>0.276</v>
       </c>
       <c r="AB61" t="n">
         <v>0.317</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.66</v>
+        <v>0.659</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
@@ -6034,15 +5245,6 @@
       <c r="AF61" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6117,15 +5319,6 @@
       <c r="AF62" t="n">
         <v>0</v>
       </c>
-      <c r="AG62" t="inlineStr"/>
-      <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6200,15 +5393,6 @@
       <c r="AF63" t="n">
         <v>0</v>
       </c>
-      <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6227,7 +5411,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -6263,35 +5447,26 @@
         <v>0.499</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="AA64" t="n">
         <v>0.254</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.284</v>
+        <v>0.283</v>
       </c>
       <c r="AC64" t="n">
-        <v>0.677</v>
+        <v>0.678</v>
       </c>
       <c r="AD64" t="n">
         <v>0.001</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.322</v>
+        <v>0.32</v>
       </c>
       <c r="AF64" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
-      <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="inlineStr"/>
-      <c r="AO64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6366,15 +5541,6 @@
       <c r="AF65" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="inlineStr"/>
-      <c r="AO65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6449,15 +5615,6 @@
       <c r="AF66" t="n">
         <v>0</v>
       </c>
-      <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr"/>
-      <c r="AO66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6532,15 +5689,6 @@
       <c r="AF67" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG67" t="inlineStr"/>
-      <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr"/>
-      <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="inlineStr"/>
-      <c r="AN67" t="inlineStr"/>
-      <c r="AO67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6615,15 +5763,6 @@
       <c r="AF68" t="n">
         <v>0</v>
       </c>
-      <c r="AG68" t="inlineStr"/>
-      <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr"/>
-      <c r="AN68" t="inlineStr"/>
-      <c r="AO68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6698,15 +5837,6 @@
       <c r="AF69" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
-      <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr"/>
-      <c r="AN69" t="inlineStr"/>
-      <c r="AO69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6781,15 +5911,6 @@
       <c r="AF70" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG70" t="inlineStr"/>
-      <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="inlineStr"/>
-      <c r="AN70" t="inlineStr"/>
-      <c r="AO70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6864,15 +5985,6 @@
       <c r="AF71" t="n">
         <v>0</v>
       </c>
-      <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
-      <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="inlineStr"/>
-      <c r="AN71" t="inlineStr"/>
-      <c r="AO71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6947,15 +6059,6 @@
       <c r="AF72" t="n">
         <v>0</v>
       </c>
-      <c r="AG72" t="inlineStr"/>
-      <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr"/>
-      <c r="AJ72" t="inlineStr"/>
-      <c r="AK72" t="inlineStr"/>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="inlineStr"/>
-      <c r="AN72" t="inlineStr"/>
-      <c r="AO72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7030,15 +6133,6 @@
       <c r="AF73" t="n">
         <v>0</v>
       </c>
-      <c r="AG73" t="inlineStr"/>
-      <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr"/>
-      <c r="AJ73" t="inlineStr"/>
-      <c r="AK73" t="inlineStr"/>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr"/>
-      <c r="AN73" t="inlineStr"/>
-      <c r="AO73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7113,15 +6207,6 @@
       <c r="AF74" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
-      <c r="AJ74" t="inlineStr"/>
-      <c r="AK74" t="inlineStr"/>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="inlineStr"/>
-      <c r="AN74" t="inlineStr"/>
-      <c r="AO74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7140,7 +6225,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1826</v>
+        <v>1837</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -7173,7 +6258,7 @@
         <v>0.321</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="Z75" t="n">
         <v>0.454</v>
@@ -7185,26 +6270,17 @@
         <v>0.254</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="AD75" t="n">
         <v>0.001</v>
       </c>
       <c r="AE75" t="n">
-        <v>0.273</v>
+        <v>0.274</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
       </c>
-      <c r="AG75" t="inlineStr"/>
-      <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
-      <c r="AJ75" t="inlineStr"/>
-      <c r="AK75" t="inlineStr"/>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="inlineStr"/>
-      <c r="AN75" t="inlineStr"/>
-      <c r="AO75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7279,15 +6355,6 @@
       <c r="AF76" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG76" t="inlineStr"/>
-      <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr"/>
-      <c r="AJ76" t="inlineStr"/>
-      <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="inlineStr"/>
-      <c r="AN76" t="inlineStr"/>
-      <c r="AO76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7362,15 +6429,6 @@
       <c r="AF77" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG77" t="inlineStr"/>
-      <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
-      <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr"/>
-      <c r="AN77" t="inlineStr"/>
-      <c r="AO77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7445,15 +6503,6 @@
       <c r="AF78" t="n">
         <v>0</v>
       </c>
-      <c r="AG78" t="inlineStr"/>
-      <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr"/>
-      <c r="AJ78" t="inlineStr"/>
-      <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="inlineStr"/>
-      <c r="AN78" t="inlineStr"/>
-      <c r="AO78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7528,15 +6577,6 @@
       <c r="AF79" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG79" t="inlineStr"/>
-      <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
-      <c r="AJ79" t="inlineStr"/>
-      <c r="AK79" t="inlineStr"/>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
-      <c r="AN79" t="inlineStr"/>
-      <c r="AO79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7611,15 +6651,6 @@
       <c r="AF80" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG80" t="inlineStr"/>
-      <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
-      <c r="AN80" t="inlineStr"/>
-      <c r="AO80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7694,15 +6725,6 @@
       <c r="AF81" t="n">
         <v>0</v>
       </c>
-      <c r="AG81" t="inlineStr"/>
-      <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
-      <c r="AJ81" t="inlineStr"/>
-      <c r="AK81" t="inlineStr"/>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr"/>
-      <c r="AN81" t="inlineStr"/>
-      <c r="AO81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7777,15 +6799,6 @@
       <c r="AF82" t="n">
         <v>0</v>
       </c>
-      <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
-      <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="inlineStr"/>
-      <c r="AN82" t="inlineStr"/>
-      <c r="AO82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7860,15 +6873,6 @@
       <c r="AF83" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="inlineStr"/>
-      <c r="AN83" t="inlineStr"/>
-      <c r="AO83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7943,15 +6947,6 @@
       <c r="AF84" t="n">
         <v>0</v>
       </c>
-      <c r="AG84" t="inlineStr"/>
-      <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr"/>
-      <c r="AJ84" t="inlineStr"/>
-      <c r="AK84" t="inlineStr"/>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="inlineStr"/>
-      <c r="AN84" t="inlineStr"/>
-      <c r="AO84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8026,15 +7021,6 @@
       <c r="AF85" t="n">
         <v>0</v>
       </c>
-      <c r="AG85" t="inlineStr"/>
-      <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="inlineStr"/>
-      <c r="AJ85" t="inlineStr"/>
-      <c r="AK85" t="inlineStr"/>
-      <c r="AL85" t="inlineStr"/>
-      <c r="AM85" t="inlineStr"/>
-      <c r="AN85" t="inlineStr"/>
-      <c r="AO85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8109,15 +7095,6 @@
       <c r="AF86" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
-      <c r="AJ86" t="inlineStr"/>
-      <c r="AK86" t="inlineStr"/>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86" t="inlineStr"/>
-      <c r="AN86" t="inlineStr"/>
-      <c r="AO86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8192,15 +7169,6 @@
       <c r="AF87" t="n">
         <v>0</v>
       </c>
-      <c r="AG87" t="inlineStr"/>
-      <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr"/>
-      <c r="AJ87" t="inlineStr"/>
-      <c r="AK87" t="inlineStr"/>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="inlineStr"/>
-      <c r="AN87" t="inlineStr"/>
-      <c r="AO87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8275,15 +7243,6 @@
       <c r="AF88" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG88" t="inlineStr"/>
-      <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr"/>
-      <c r="AJ88" t="inlineStr"/>
-      <c r="AK88" t="inlineStr"/>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88" t="inlineStr"/>
-      <c r="AN88" t="inlineStr"/>
-      <c r="AO88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8358,15 +7317,6 @@
       <c r="AF89" t="n">
         <v>0</v>
       </c>
-      <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
-      <c r="AN89" t="inlineStr"/>
-      <c r="AO89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8441,15 +7391,6 @@
       <c r="AF90" t="n">
         <v>0.001</v>
       </c>
-      <c r="AG90" t="inlineStr"/>
-      <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr"/>
-      <c r="AJ90" t="inlineStr"/>
-      <c r="AK90" t="inlineStr"/>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90" t="inlineStr"/>
-      <c r="AN90" t="inlineStr"/>
-      <c r="AO90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8524,15 +7465,6 @@
       <c r="AF91" t="n">
         <v>0.002</v>
       </c>
-      <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
-      <c r="AJ91" t="inlineStr"/>
-      <c r="AK91" t="inlineStr"/>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91" t="inlineStr"/>
-      <c r="AN91" t="inlineStr"/>
-      <c r="AO91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8606,400 +7538,6 @@
       </c>
       <c r="AF92" t="n">
         <v>0.001</v>
-      </c>
-      <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="inlineStr"/>
-      <c r="AJ92" t="inlineStr"/>
-      <c r="AK92" t="inlineStr"/>
-      <c r="AL92" t="inlineStr"/>
-      <c r="AM92" t="inlineStr"/>
-      <c r="AN92" t="inlineStr"/>
-      <c r="AO92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Belgian Pro League</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>Fixture Predictions</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
-      <c r="AB93" t="inlineStr"/>
-      <c r="AC93" t="inlineStr"/>
-      <c r="AD93" t="inlineStr"/>
-      <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr"/>
-      <c r="AG93" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN93" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO93" t="n">
-        <v>2.333</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Fixture Predictions</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
-      <c r="AB94" t="inlineStr"/>
-      <c r="AC94" t="inlineStr"/>
-      <c r="AD94" t="inlineStr"/>
-      <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH94" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="AK94" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="AL94" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="AM94" t="n">
-        <v>10</v>
-      </c>
-      <c r="AN94" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO94" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Fixture Predictions</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
-      <c r="AB95" t="inlineStr"/>
-      <c r="AC95" t="inlineStr"/>
-      <c r="AD95" t="inlineStr"/>
-      <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH95" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI95" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="AJ95" t="n">
-        <v>0.408</v>
-      </c>
-      <c r="AK95" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="AL95" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="AM95" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN95" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO95" t="n">
-        <v>1.857</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Tier 1 - Elite Europe</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Fixture Predictions</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
-      <c r="AC96" t="inlineStr"/>
-      <c r="AD96" t="inlineStr"/>
-      <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="AK96" t="n">
-        <v>0.954</v>
-      </c>
-      <c r="AL96" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AM96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO96" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Tier 2 - Europe Depth</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>La Liga 2</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Fixture Predictions</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr"/>
-      <c r="AC97" t="inlineStr"/>
-      <c r="AD97" t="inlineStr"/>
-      <c r="AE97" t="inlineStr"/>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH97" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI97" t="n">
-        <v>0.694</v>
-      </c>
-      <c r="AJ97" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="AK97" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="AL97" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="AM97" t="n">
-        <v>11</v>
-      </c>
-      <c r="AN97" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO97" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9059,7 +7597,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:43:13</t>
+          <t>2026-05-25 14:40:26</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -9082,11 +7620,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:43:54</t>
+          <t>2026-05-25 14:41:08</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="4">
@@ -9105,7 +7643,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:43:40</t>
+          <t>2026-05-25 14:40:53</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -9128,11 +7666,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:45:48</t>
+          <t>2026-05-25 14:43:04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17.88</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="6">
@@ -9151,11 +7689,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:45:50</t>
+          <t>2026-05-25 14:34:59</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/football/exports/reporting/football_model_performance_dashboard.xlsx
+++ b/data/football/exports/reporting/football_model_performance_dashboard.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:43:06</t>
+          <t>2026-05-26 14:31:40</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:42:10</t>
+          <t>2026-05-26 14:30:48</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:40:26</t>
+          <t>2026-05-26 14:29:14</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:41:08</t>
+          <t>2026-05-26 14:29:54</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:40:53</t>
+          <t>2026-05-26 14:29:40</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:43:04</t>
+          <t>2026-05-26 14:31:38</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:59</t>
+          <t>2026-05-26 14:24:14</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/data/football/exports/reporting/football_model_performance_dashboard.xlsx
+++ b/data/football/exports/reporting/football_model_performance_dashboard.xlsx
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>58059</v>
       </c>
     </row>
     <row r="3">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>58058</v>
       </c>
     </row>
     <row r="5">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75345</v>
+        <v>75424</v>
       </c>
     </row>
     <row r="6">
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:31:40</t>
+          <t>2026-05-27 15:07:10</t>
         </is>
       </c>
     </row>
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57980</v>
+        <v>58059</v>
       </c>
       <c r="E2" t="n">
         <v>0.778</v>
       </c>
       <c r="F2" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="G2" t="n">
         <v>0.73</v>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57980</v>
+        <v>58059</v>
       </c>
       <c r="E3" t="n">
         <v>0.596</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57980</v>
+        <v>58059</v>
       </c>
       <c r="E4" t="n">
         <v>0.386</v>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57980</v>
+        <v>58059</v>
       </c>
       <c r="E5" t="n">
-        <v>0.611</v>
+        <v>0.612</v>
       </c>
       <c r="F5" t="n">
-        <v>0.529</v>
+        <v>0.53</v>
       </c>
       <c r="G5" t="n">
         <v>0.547</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57979</v>
+        <v>58058</v>
       </c>
       <c r="E10" t="n">
-        <v>0.396</v>
+        <v>0.397</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75345</v>
+        <v>75424</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:30:48</t>
+          <t>2026-05-27 15:06:14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4180</v>
+        <v>4181</v>
       </c>
       <c r="E22" t="n">
         <v>2.067</v>
@@ -2649,31 +2649,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2817</v>
+        <v>2827</v>
       </c>
       <c r="E24" t="n">
-        <v>2.477</v>
+        <v>2.479</v>
       </c>
       <c r="F24" t="n">
         <v>0.741</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.57</v>
+        <v>0.571</v>
       </c>
       <c r="I24" t="n">
         <v>0.712</v>
       </c>
       <c r="J24" t="n">
-        <v>0.583</v>
+        <v>0.582</v>
       </c>
       <c r="K24" t="n">
         <v>0.78</v>
       </c>
       <c r="L24" t="n">
-        <v>0.569</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="E25" t="n">
         <v>2.993</v>
@@ -2726,7 +2726,7 @@
         <v>0.828</v>
       </c>
       <c r="G25" t="n">
-        <v>0.646</v>
+        <v>0.647</v>
       </c>
       <c r="H25" t="n">
         <v>0.672</v>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E27" t="n">
-        <v>2.92</v>
+        <v>2.918</v>
       </c>
       <c r="F27" t="n">
         <v>0.8179999999999999</v>
@@ -2871,13 +2871,13 @@
         <v>0.793</v>
       </c>
       <c r="J27" t="n">
-        <v>0.581</v>
+        <v>0.579</v>
       </c>
       <c r="K27" t="n">
-        <v>0.673</v>
+        <v>0.675</v>
       </c>
       <c r="L27" t="n">
-        <v>0.599</v>
+        <v>0.598</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2921,10 +2921,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="E28" t="n">
-        <v>2.451</v>
+        <v>2.453</v>
       </c>
       <c r="F28" t="n">
         <v>0.737</v>
@@ -2933,7 +2933,7 @@
         <v>0.5580000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>0.696</v>
@@ -2945,7 +2945,7 @@
         <v>0.763</v>
       </c>
       <c r="L28" t="n">
-        <v>0.553</v>
+        <v>0.554</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E30" t="n">
         <v>2.827</v>
@@ -3078,7 +3078,7 @@
         <v>0.544</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="L30" t="n">
         <v>0.541</v>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="E31" t="n">
         <v>3.048</v>
@@ -3140,13 +3140,13 @@
         <v>0.677</v>
       </c>
       <c r="I31" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="J31" t="n">
-        <v>0.604</v>
+        <v>0.603</v>
       </c>
       <c r="K31" t="n">
-        <v>0.628</v>
+        <v>0.629</v>
       </c>
       <c r="L31" t="n">
         <v>0.597</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="E32" t="n">
         <v>2.647</v>
@@ -3208,13 +3208,13 @@
         <v>0.61</v>
       </c>
       <c r="I32" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="J32" t="n">
-        <v>0.506</v>
+        <v>0.507</v>
       </c>
       <c r="K32" t="n">
-        <v>0.722</v>
+        <v>0.721</v>
       </c>
       <c r="L32" t="n">
         <v>0.52</v>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="E33" t="n">
-        <v>2.472</v>
+        <v>2.47</v>
       </c>
       <c r="F33" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="G33" t="n">
         <v>0.5610000000000001</v>
@@ -3282,7 +3282,7 @@
         <v>0.521</v>
       </c>
       <c r="K33" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="L33" t="n">
         <v>0.496</v>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1752</v>
+        <v>1760</v>
       </c>
       <c r="E35" t="n">
-        <v>2.809</v>
+        <v>2.81</v>
       </c>
       <c r="F35" t="n">
         <v>0.799</v>
@@ -3412,16 +3412,16 @@
         <v>0.629</v>
       </c>
       <c r="I35" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="J35" t="n">
-        <v>0.573</v>
+        <v>0.574</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7</v>
+        <v>0.701</v>
       </c>
       <c r="L35" t="n">
-        <v>0.584</v>
+        <v>0.585</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3858</v>
+        <v>3873</v>
       </c>
       <c r="E37" t="n">
-        <v>2.97</v>
+        <v>2.971</v>
       </c>
       <c r="F37" t="n">
         <v>0.828</v>
@@ -3548,16 +3548,16 @@
         <v>0.679</v>
       </c>
       <c r="I37" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="J37" t="n">
-        <v>0.602</v>
+        <v>0.603</v>
       </c>
       <c r="K37" t="n">
         <v>0.654</v>
       </c>
       <c r="L37" t="n">
-        <v>0.605</v>
+        <v>0.606</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4180</v>
+        <v>4181</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
@@ -6418,7 +6418,7 @@
         <v>0.252</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AD77" t="n">
         <v>0.007</v>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2817</v>
+        <v>2827</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
@@ -6560,13 +6560,13 @@
         <v>0.476</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.266</v>
+        <v>0.265</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.258</v>
+        <v>0.259</v>
       </c>
       <c r="AC79" t="n">
-        <v>0.673</v>
+        <v>0.674</v>
       </c>
       <c r="AD79" t="n">
         <v>0.002</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1850</v>
+        <v>1858</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
@@ -6625,28 +6625,28 @@
         <v>0.27</v>
       </c>
       <c r="X80" t="n">
-        <v>0.328</v>
+        <v>0.327</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="AA80" t="n">
         <v>0.248</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.3</v>
+        <v>0.301</v>
       </c>
       <c r="AC80" t="n">
-        <v>0.638</v>
+        <v>0.639</v>
       </c>
       <c r="AD80" t="n">
         <v>0.003</v>
       </c>
       <c r="AE80" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="AF80" t="n">
         <v>0.001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
@@ -6770,22 +6770,22 @@
         <v>0.401</v>
       </c>
       <c r="W82" t="n">
-        <v>0.27</v>
+        <v>0.271</v>
       </c>
       <c r="X82" t="n">
-        <v>0.329</v>
+        <v>0.328</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.536</v>
+        <v>0.538</v>
       </c>
       <c r="Z82" t="n">
-        <v>0.431</v>
+        <v>0.433</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.242</v>
+        <v>0.24</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.328</v>
+        <v>0.327</v>
       </c>
       <c r="AC82" t="n">
         <v>0.653</v>
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1349</v>
+        <v>1356</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
@@ -6850,10 +6850,10 @@
         <v>0.327</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.5</v>
+        <v>0.498</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.431</v>
+        <v>0.429</v>
       </c>
       <c r="AA83" t="n">
         <v>0.282</v>
@@ -6862,13 +6862,13 @@
         <v>0.288</v>
       </c>
       <c r="AC83" t="n">
-        <v>0.652</v>
+        <v>0.653</v>
       </c>
       <c r="AD83" t="n">
         <v>0.001</v>
       </c>
       <c r="AE83" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="AF83" t="n">
         <v>0.002</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -7001,7 +7001,7 @@
         <v>0.479</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="AA85" t="n">
         <v>0.258</v>
@@ -7010,7 +7010,7 @@
         <v>0.282</v>
       </c>
       <c r="AC85" t="n">
-        <v>0.696</v>
+        <v>0.695</v>
       </c>
       <c r="AD85" t="n">
         <v>0.001</v>
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
@@ -7075,16 +7075,16 @@
         <v>0.549</v>
       </c>
       <c r="Z86" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="AA86" t="n">
         <v>0.209</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="AC86" t="n">
-        <v>0.658</v>
+        <v>0.657</v>
       </c>
       <c r="AD86" t="n">
         <v>0</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
@@ -7146,25 +7146,25 @@
         <v>0.324</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
       <c r="Z87" t="n">
-        <v>0.437</v>
+        <v>0.439</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.274</v>
+        <v>0.275</v>
       </c>
       <c r="AB87" t="n">
-        <v>0.289</v>
+        <v>0.287</v>
       </c>
       <c r="AC87" t="n">
-        <v>0.705</v>
+        <v>0.708</v>
       </c>
       <c r="AD87" t="n">
         <v>0.001</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.294</v>
+        <v>0.292</v>
       </c>
       <c r="AF87" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
@@ -7220,19 +7220,19 @@
         <v>0.324</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.285</v>
+        <v>0.288</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.281</v>
+        <v>0.28</v>
       </c>
       <c r="AC88" t="n">
-        <v>0.694</v>
+        <v>0.695</v>
       </c>
       <c r="AD88" t="n">
         <v>0.001</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1752</v>
+        <v>1760</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -7368,7 +7368,7 @@
         <v>0.329</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.516</v>
+        <v>0.515</v>
       </c>
       <c r="Z90" t="n">
         <v>0.439</v>
@@ -7380,13 +7380,13 @@
         <v>0.341</v>
       </c>
       <c r="AC90" t="n">
-        <v>0.644</v>
+        <v>0.645</v>
       </c>
       <c r="AD90" t="n">
         <v>0.002</v>
       </c>
       <c r="AE90" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="AF90" t="n">
         <v>0.001</v>
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3858</v>
+        <v>3873</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
@@ -7510,7 +7510,7 @@
         <v>0.4</v>
       </c>
       <c r="W92" t="n">
-        <v>0.275</v>
+        <v>0.276</v>
       </c>
       <c r="X92" t="n">
         <v>0.325</v>
@@ -7534,7 +7534,7 @@
         <v>0.003</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="AF92" t="n">
         <v>0.001</v>
@@ -7597,11 +7597,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:29:14</t>
+          <t>2026-05-27 15:04:31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.41</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="3">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:29:54</t>
+          <t>2026-05-27 15:05:13</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7643,11 +7643,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:29:40</t>
+          <t>2026-05-27 15:04:58</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="5">
@@ -7666,11 +7666,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:31:38</t>
+          <t>2026-05-27 15:07:08</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>17.89</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="6">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:24:14</t>
+          <t>2026-05-27 14:59:08</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/data/football/exports/reporting/football_model_performance_dashboard.xlsx
+++ b/data/football/exports/reporting/football_model_performance_dashboard.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-27 15:07:10</t>
+          <t>2026-05-28 09:02:51</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-27 15:06:14</t>
+          <t>2026-05-28 09:01:54</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-27 15:04:31</t>
+          <t>2026-05-28 09:00:19</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-27 15:05:13</t>
+          <t>2026-05-28 09:00:59</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-27 15:04:58</t>
+          <t>2026-05-28 09:00:45</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-27 15:07:08</t>
+          <t>2026-05-28 09:02:48</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:59:08</t>
+          <t>2026-05-28 08:55:11</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/data/football/exports/reporting/football_model_performance_dashboard.xlsx
+++ b/data/football/exports/reporting/football_model_performance_dashboard.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-28 09:02:51</t>
+          <t>2026-05-28 17:31:14</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-28 09:01:54</t>
+          <t>2026-05-28 17:30:19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-28 09:00:19</t>
+          <t>2026-05-28 17:28:37</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-28 09:00:59</t>
+          <t>2026-05-28 17:29:18</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-28 09:00:45</t>
+          <t>2026-05-28 17:29:04</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-28 09:02:48</t>
+          <t>2026-05-28 17:31:12</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:55:11</t>
+          <t>2026-05-28 17:23:18</t>
         </is>
       </c>
       <c r="E6" t="n">

--- a/data/football/exports/reporting/football_model_performance_dashboard.xlsx
+++ b/data/football/exports/reporting/football_model_performance_dashboard.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:31:14</t>
+          <t>2026-05-28 19:58:22</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:30:19</t>
+          <t>2026-05-28 19:57:25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:28:37</t>
+          <t>2026-05-28 19:55:46</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:29:18</t>
+          <t>2026-05-28 19:56:30</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:29:04</t>
+          <t>2026-05-28 19:56:14</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:31:12</t>
+          <t>2026-05-28 19:58:20</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:23:18</t>
+          <t>2026-05-28 19:50:39</t>
         </is>
       </c>
       <c r="E6" t="n">
